--- a/logs/nzd/raw/C50.xlsx
+++ b/logs/nzd/raw/C50.xlsx
@@ -9057,6 +9057,77 @@
         <v>51201</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="28">
+        <v>46265</v>
+      </c>
+      <c r="B122" s="16">
+        <v>454671</v>
+      </c>
+      <c r="C122" s="16">
+        <v>134977</v>
+      </c>
+      <c r="D122" s="16">
+        <v>9174</v>
+      </c>
+      <c r="E122" s="16">
+        <v>125803</v>
+      </c>
+      <c r="F122" s="16">
+        <v>319694</v>
+      </c>
+      <c r="G122" s="16">
+        <v>111189</v>
+      </c>
+      <c r="H122" s="16">
+        <v>208505</v>
+      </c>
+      <c r="I122" s="16">
+        <v>645415</v>
+      </c>
+      <c r="J122" s="16">
+        <v>20753</v>
+      </c>
+      <c r="K122" s="16">
+        <v>63552</v>
+      </c>
+      <c r="L122" s="16">
+        <v>42800</v>
+      </c>
+      <c r="M122" s="16">
+        <v>624663</v>
+      </c>
+      <c r="N122" s="16">
+        <v>612777</v>
+      </c>
+      <c r="O122" s="16">
+        <v>9066</v>
+      </c>
+      <c r="P122" s="16">
+        <v>2820</v>
+      </c>
+      <c r="Q122" s="16">
+        <v>-80376</v>
+      </c>
+      <c r="R122" s="16">
+        <v>95853</v>
+      </c>
+      <c r="S122" s="16">
+        <v>176229</v>
+      </c>
+      <c r="T122" s="16">
+        <v>-75560</v>
+      </c>
+      <c r="U122" s="16">
+        <v>-34809</v>
+      </c>
+      <c r="V122" s="16">
+        <v>17176</v>
+      </c>
+      <c r="W122" s="16">
+        <v>51985</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B5" location="'Series Definitions'!R2C3"/>
@@ -9124,7 +9195,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="27">
-        <v>46265</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="5"/>
